--- a/iso27090/modelos/matriz-ameacas-iso27090.xlsx
+++ b/iso27090/modelos/matriz-ameacas-iso27090.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="70">
   <si>
     <t xml:space="preserve">Matriz de modelagem de ameaças · ISO/IEC 27090 cláusula 6</t>
   </si>
@@ -52,6 +52,9 @@
   </si>
   <si>
     <t xml:space="preserve">Fonte: guia prático ISO/IEC 27090 em andre0silva.github.io/iso27090. Material de apoio; não reproduz o texto da norma.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licença: CC BY-NC 4.0 (https://creativecommons.org/licenses/by-nc/4.0/deed.pt-br). © 2026 André Ferreira. Uso livre com crédito ao autor, sem fins comerciais. Fornecido sem garantia.</t>
   </si>
   <si>
     <t xml:space="preserve">Sistema (ID do inventário)</t>
@@ -797,7 +800,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -846,6 +849,11 @@
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -886,66 +894,66 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -970,13 +978,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -1001,13 +1009,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -1032,13 +1040,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -1063,13 +1071,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -1094,13 +1102,13 @@
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -1125,19 +1133,19 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>3</v>
@@ -1154,41 +1162,41 @@
         <v>Alto</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>4</v>
@@ -1205,41 +1213,41 @@
         <v>Alto</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>2</v>
@@ -1257,19 +1265,19 @@
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
@@ -1277,10 +1285,10 @@
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
       <c r="B11" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -1306,10 +1314,10 @@
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
       <c r="B12" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -1335,10 +1343,10 @@
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
       <c r="B13" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -1364,10 +1372,10 @@
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
       <c r="B14" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
@@ -1393,10 +1401,10 @@
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
       <c r="B15" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -1422,10 +1430,10 @@
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
       <c r="B16" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -1451,10 +1459,10 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
       <c r="B17" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -1480,10 +1488,10 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
       <c r="B18" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
@@ -1509,10 +1517,10 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
       <c r="B19" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -1538,10 +1546,10 @@
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
       <c r="B20" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -1567,10 +1575,10 @@
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
       <c r="B21" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -1596,10 +1604,10 @@
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
       <c r="B22" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -1625,10 +1633,10 @@
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
       <c r="B23" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
@@ -1654,10 +1662,10 @@
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
       <c r="B24" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -1683,10 +1691,10 @@
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5"/>
       <c r="B25" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -1712,10 +1720,10 @@
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5"/>
       <c r="B26" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -1741,10 +1749,10 @@
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5"/>
       <c r="B27" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
@@ -1770,10 +1778,10 @@
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5"/>
       <c r="B28" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -1799,10 +1807,10 @@
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5"/>
       <c r="B29" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
@@ -1828,10 +1836,10 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
       <c r="B30" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
@@ -1857,10 +1865,10 @@
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
       <c r="B31" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
@@ -1886,10 +1894,10 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5"/>
       <c r="B32" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
@@ -1915,10 +1923,10 @@
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5"/>
       <c r="B33" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
@@ -1944,10 +1952,10 @@
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5"/>
       <c r="B34" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
@@ -1973,10 +1981,10 @@
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5"/>
       <c r="B35" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -2002,10 +2010,10 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5"/>
       <c r="B36" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
@@ -2031,10 +2039,10 @@
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5"/>
       <c r="B37" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
@@ -2060,10 +2068,10 @@
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5"/>
       <c r="B38" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
@@ -2089,10 +2097,10 @@
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5"/>
       <c r="B39" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
@@ -2118,10 +2126,10 @@
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5"/>
       <c r="B40" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -2147,10 +2155,10 @@
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5"/>
       <c r="B41" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
@@ -2176,10 +2184,10 @@
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5"/>
       <c r="B42" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
@@ -2205,10 +2213,10 @@
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
       <c r="B43" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
@@ -2234,10 +2242,10 @@
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5"/>
       <c r="B44" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
@@ -2263,10 +2271,10 @@
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5"/>
       <c r="B45" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
@@ -2292,10 +2300,10 @@
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5"/>
       <c r="B46" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
@@ -2321,10 +2329,10 @@
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5"/>
       <c r="B47" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
@@ -2350,10 +2358,10 @@
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5"/>
       <c r="B48" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
@@ -2379,10 +2387,10 @@
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5"/>
       <c r="B49" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
@@ -2408,10 +2416,10 @@
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5"/>
       <c r="B50" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
@@ -2437,10 +2445,10 @@
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5"/>
       <c r="B51" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
@@ -2466,10 +2474,10 @@
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5"/>
       <c r="B52" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
@@ -2495,10 +2503,10 @@
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5"/>
       <c r="B53" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
@@ -2524,10 +2532,10 @@
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5"/>
       <c r="B54" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
@@ -2553,10 +2561,10 @@
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5"/>
       <c r="B55" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
@@ -2582,10 +2590,10 @@
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5"/>
       <c r="B56" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
@@ -2611,10 +2619,10 @@
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5"/>
       <c r="B57" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
@@ -2640,10 +2648,10 @@
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5"/>
       <c r="B58" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
@@ -2669,10 +2677,10 @@
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5"/>
       <c r="B59" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
@@ -2698,10 +2706,10 @@
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5"/>
       <c r="B60" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
@@ -2727,10 +2735,10 @@
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5"/>
       <c r="B61" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
@@ -2756,10 +2764,10 @@
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5"/>
       <c r="B62" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
@@ -2785,10 +2793,10 @@
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5"/>
       <c r="B63" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
@@ -2814,10 +2822,10 @@
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5"/>
       <c r="B64" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
@@ -2843,10 +2851,10 @@
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5"/>
       <c r="B65" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
@@ -2872,10 +2880,10 @@
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5"/>
       <c r="B66" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5"/>
@@ -2901,10 +2909,10 @@
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5"/>
       <c r="B67" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
@@ -2930,10 +2938,10 @@
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5"/>
       <c r="B68" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5"/>
@@ -2959,10 +2967,10 @@
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5"/>
       <c r="B69" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
@@ -2988,10 +2996,10 @@
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5"/>
       <c r="B70" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5"/>
@@ -3017,10 +3025,10 @@
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5"/>
       <c r="B71" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5"/>
@@ -3046,10 +3054,10 @@
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5"/>
       <c r="B72" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5"/>
@@ -3075,10 +3083,10 @@
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5"/>
       <c r="B73" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
@@ -3104,10 +3112,10 @@
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5"/>
       <c r="B74" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
@@ -3133,10 +3141,10 @@
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5"/>
       <c r="B75" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
@@ -3162,10 +3170,10 @@
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5"/>
       <c r="B76" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
@@ -3191,10 +3199,10 @@
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5"/>
       <c r="B77" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
@@ -3220,10 +3228,10 @@
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5"/>
       <c r="B78" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
@@ -3249,10 +3257,10 @@
     <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5"/>
       <c r="B79" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
@@ -3278,10 +3286,10 @@
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5"/>
       <c r="B80" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
@@ -3307,10 +3315,10 @@
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5"/>
       <c r="B81" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
@@ -3336,10 +3344,10 @@
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5"/>
       <c r="B82" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D82" s="5"/>
       <c r="E82" s="5"/>
@@ -3365,10 +3373,10 @@
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5"/>
       <c r="B83" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
@@ -3394,10 +3402,10 @@
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5"/>
       <c r="B84" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
@@ -3423,10 +3431,10 @@
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="5"/>
       <c r="B85" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
@@ -3452,10 +3460,10 @@
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="5"/>
       <c r="B86" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
@@ -3481,10 +3489,10 @@
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5"/>
       <c r="B87" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
@@ -3510,10 +3518,10 @@
     <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="5"/>
       <c r="B88" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
@@ -3539,10 +3547,10 @@
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="5"/>
       <c r="B89" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
@@ -3568,10 +3576,10 @@
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="5"/>
       <c r="B90" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
@@ -3597,10 +3605,10 @@
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5"/>
       <c r="B91" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
@@ -3626,10 +3634,10 @@
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="5"/>
       <c r="B92" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
@@ -3655,10 +3663,10 @@
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="5"/>
       <c r="B93" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
@@ -3684,10 +3692,10 @@
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="5"/>
       <c r="B94" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
@@ -3713,10 +3721,10 @@
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="5"/>
       <c r="B95" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
@@ -3742,10 +3750,10 @@
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="5"/>
       <c r="B96" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
@@ -3771,10 +3779,10 @@
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="5"/>
       <c r="B97" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
@@ -3800,10 +3808,10 @@
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="5"/>
       <c r="B98" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
@@ -3829,10 +3837,10 @@
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="5"/>
       <c r="B99" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
@@ -3858,10 +3866,10 @@
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="5"/>
       <c r="B100" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
@@ -3939,46 +3947,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B3" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B4" s="8" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3986,7 +3994,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3994,7 +4002,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
